--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374061</v>
+        <v>124374229</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467334</v>
+        <v>467270</v>
       </c>
       <c r="R2" t="n">
-        <v>6720705</v>
+        <v>6720712</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -771,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374229</v>
+        <v>124374084</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467270</v>
+        <v>467339</v>
       </c>
       <c r="R3" t="n">
-        <v>6720712</v>
+        <v>6720715</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -882,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374100</v>
+        <v>124374061</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -935,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467303</v>
+        <v>467334</v>
       </c>
       <c r="R4" t="n">
-        <v>6720698</v>
+        <v>6720705</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374210</v>
+        <v>124373923</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467276</v>
+        <v>467320</v>
       </c>
       <c r="R5" t="n">
-        <v>6720709</v>
+        <v>6720727</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1121,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374084</v>
+        <v>124374210</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,35 +1129,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467339</v>
+        <v>467276</v>
       </c>
       <c r="R6" t="n">
-        <v>6720715</v>
+        <v>6720709</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1232,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124373923</v>
+        <v>124374100</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,30 +1235,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467320</v>
+        <v>467303</v>
       </c>
       <c r="R7" t="n">
-        <v>6720727</v>
+        <v>6720698</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374229</v>
+        <v>124374100</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467270</v>
+        <v>467303</v>
       </c>
       <c r="R2" t="n">
-        <v>6720712</v>
+        <v>6720698</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374084</v>
+        <v>124374061</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -820,10 +825,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467339</v>
+        <v>467334</v>
       </c>
       <c r="R3" t="n">
-        <v>6720715</v>
+        <v>6720705</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374061</v>
+        <v>124374084</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -931,14 +940,10 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467334</v>
+        <v>467339</v>
       </c>
       <c r="R4" t="n">
-        <v>6720705</v>
+        <v>6720715</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124373923</v>
+        <v>124374210</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467320</v>
+        <v>467276</v>
       </c>
       <c r="R5" t="n">
-        <v>6720727</v>
+        <v>6720709</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374210</v>
+        <v>124374229</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,30 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467276</v>
+        <v>467270</v>
       </c>
       <c r="R6" t="n">
-        <v>6720709</v>
+        <v>6720712</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1204,7 +1214,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374100</v>
+        <v>124373923</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,39 +1244,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467303</v>
+        <v>467320</v>
       </c>
       <c r="R7" t="n">
-        <v>6720698</v>
+        <v>6720727</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374100</v>
+        <v>124374229</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467303</v>
+        <v>467270</v>
       </c>
       <c r="R2" t="n">
-        <v>6720698</v>
+        <v>6720712</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -771,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -905,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374084</v>
+        <v>124374210</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +912,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467339</v>
+        <v>467276</v>
       </c>
       <c r="R4" t="n">
-        <v>6720715</v>
+        <v>6720709</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1016,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374210</v>
+        <v>124374084</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,30 +1018,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467276</v>
+        <v>467339</v>
       </c>
       <c r="R5" t="n">
-        <v>6720709</v>
+        <v>6720715</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1122,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374229</v>
+        <v>124373923</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1129,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467270</v>
+        <v>467320</v>
       </c>
       <c r="R6" t="n">
-        <v>6720712</v>
+        <v>6720727</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1214,6 +1204,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124373923</v>
+        <v>124374100</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,30 +1235,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467320</v>
+        <v>467303</v>
       </c>
       <c r="R7" t="n">
-        <v>6720727</v>
+        <v>6720698</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374061</v>
+        <v>124374084</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -820,14 +820,10 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467334</v>
+        <v>467339</v>
       </c>
       <c r="R3" t="n">
-        <v>6720705</v>
+        <v>6720715</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374210</v>
+        <v>124373923</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467276</v>
+        <v>467320</v>
       </c>
       <c r="R4" t="n">
-        <v>6720709</v>
+        <v>6720727</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374084</v>
+        <v>124374061</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1041,10 +1037,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467339</v>
+        <v>467334</v>
       </c>
       <c r="R5" t="n">
-        <v>6720715</v>
+        <v>6720705</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124373923</v>
+        <v>124374100</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,30 +1129,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467320</v>
+        <v>467303</v>
       </c>
       <c r="R6" t="n">
-        <v>6720727</v>
+        <v>6720698</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1223,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374100</v>
+        <v>124374210</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,39 +1244,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467303</v>
+        <v>467276</v>
       </c>
       <c r="R7" t="n">
-        <v>6720698</v>
+        <v>6720709</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374229</v>
+        <v>124374084</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467270</v>
+        <v>467339</v>
       </c>
       <c r="R2" t="n">
-        <v>6720712</v>
+        <v>6720715</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374084</v>
+        <v>124374229</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467339</v>
+        <v>467270</v>
       </c>
       <c r="R3" t="n">
-        <v>6720715</v>
+        <v>6720712</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374084</v>
+        <v>124374229</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467339</v>
+        <v>467270</v>
       </c>
       <c r="R2" t="n">
-        <v>6720715</v>
+        <v>6720712</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374229</v>
+        <v>124373923</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +797,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467270</v>
+        <v>467320</v>
       </c>
       <c r="R3" t="n">
-        <v>6720712</v>
+        <v>6720727</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124373923</v>
+        <v>124374100</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +903,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467320</v>
+        <v>467303</v>
       </c>
       <c r="R4" t="n">
-        <v>6720727</v>
+        <v>6720698</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374061</v>
+        <v>124374210</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,39 +1018,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467334</v>
+        <v>467276</v>
       </c>
       <c r="R5" t="n">
-        <v>6720705</v>
+        <v>6720709</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374100</v>
+        <v>124374061</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1152,7 +1147,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1169,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467303</v>
+        <v>467334</v>
       </c>
       <c r="R6" t="n">
-        <v>6720698</v>
+        <v>6720705</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1232,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374210</v>
+        <v>124374084</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,30 +1239,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467276</v>
+        <v>467339</v>
       </c>
       <c r="R7" t="n">
-        <v>6720709</v>
+        <v>6720715</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374229</v>
+        <v>124373923</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467270</v>
+        <v>467320</v>
       </c>
       <c r="R2" t="n">
-        <v>6720712</v>
+        <v>6720727</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124373923</v>
+        <v>124374229</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,30 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467320</v>
+        <v>467270</v>
       </c>
       <c r="R3" t="n">
-        <v>6720727</v>
+        <v>6720712</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374229</v>
+        <v>124374061</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +793,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467270</v>
+        <v>467334</v>
       </c>
       <c r="R3" t="n">
-        <v>6720712</v>
+        <v>6720705</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374100</v>
+        <v>124374210</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,39 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467303</v>
+        <v>467276</v>
       </c>
       <c r="R4" t="n">
-        <v>6720698</v>
+        <v>6720709</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374210</v>
+        <v>124374229</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,30 +1014,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467276</v>
+        <v>467270</v>
       </c>
       <c r="R5" t="n">
-        <v>6720709</v>
+        <v>6720712</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1093,7 +1094,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374061</v>
+        <v>124374084</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1147,14 +1147,10 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1164,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467334</v>
+        <v>467339</v>
       </c>
       <c r="R6" t="n">
-        <v>6720705</v>
+        <v>6720715</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1227,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374084</v>
+        <v>124374100</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1265,7 +1261,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467339</v>
+        <v>467303</v>
       </c>
       <c r="R7" t="n">
-        <v>6720715</v>
+        <v>6720698</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124373923</v>
+        <v>124374210</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467320</v>
+        <v>467276</v>
       </c>
       <c r="R2" t="n">
-        <v>6720727</v>
+        <v>6720709</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374210</v>
+        <v>124373923</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467276</v>
+        <v>467320</v>
       </c>
       <c r="R4" t="n">
-        <v>6720709</v>
+        <v>6720727</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374229</v>
+        <v>124374100</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,35 +1014,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467270</v>
+        <v>467303</v>
       </c>
       <c r="R5" t="n">
-        <v>6720712</v>
+        <v>6720698</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,6 +1098,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1223,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374100</v>
+        <v>124374229</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,39 +1240,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467303</v>
+        <v>467270</v>
       </c>
       <c r="R7" t="n">
-        <v>6720698</v>
+        <v>6720712</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1319,7 +1320,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374210</v>
+        <v>124374229</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467276</v>
+        <v>467270</v>
       </c>
       <c r="R2" t="n">
-        <v>6720709</v>
+        <v>6720712</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374061</v>
+        <v>124373923</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +797,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467334</v>
+        <v>467320</v>
       </c>
       <c r="R3" t="n">
-        <v>6720705</v>
+        <v>6720727</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124373923</v>
+        <v>124374061</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +903,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467320</v>
+        <v>467334</v>
       </c>
       <c r="R4" t="n">
-        <v>6720727</v>
+        <v>6720705</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1228,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374229</v>
+        <v>124374210</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,35 +1244,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1276,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467270</v>
+        <v>467276</v>
       </c>
       <c r="R7" t="n">
-        <v>6720712</v>
+        <v>6720709</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1320,6 +1319,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374229</v>
+        <v>124374210</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467270</v>
+        <v>467276</v>
       </c>
       <c r="R2" t="n">
-        <v>6720712</v>
+        <v>6720709</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124373923</v>
+        <v>124374229</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,30 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467320</v>
+        <v>467270</v>
       </c>
       <c r="R3" t="n">
-        <v>6720727</v>
+        <v>6720712</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374100</v>
+        <v>124374084</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,11 +1044,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1058,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467303</v>
+        <v>467339</v>
       </c>
       <c r="R5" t="n">
-        <v>6720698</v>
+        <v>6720715</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1121,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374084</v>
+        <v>124374100</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1159,7 +1155,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467339</v>
+        <v>467303</v>
       </c>
       <c r="R6" t="n">
-        <v>6720715</v>
+        <v>6720698</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374210</v>
+        <v>124373923</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467276</v>
+        <v>467320</v>
       </c>
       <c r="R7" t="n">
-        <v>6720709</v>
+        <v>6720727</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374210</v>
+        <v>124374084</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467276</v>
+        <v>467339</v>
       </c>
       <c r="R2" t="n">
-        <v>6720709</v>
+        <v>6720715</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -1006,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374084</v>
+        <v>124373923</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,35 +1023,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467339</v>
+        <v>467320</v>
       </c>
       <c r="R5" t="n">
-        <v>6720715</v>
+        <v>6720727</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124373923</v>
+        <v>124374210</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467320</v>
+        <v>467276</v>
       </c>
       <c r="R7" t="n">
-        <v>6720727</v>
+        <v>6720709</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374084</v>
+        <v>124374100</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -713,7 +713,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467339</v>
+        <v>467303</v>
       </c>
       <c r="R2" t="n">
-        <v>6720715</v>
+        <v>6720698</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -896,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374061</v>
+        <v>124374210</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,39 +912,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467334</v>
+        <v>467276</v>
       </c>
       <c r="R4" t="n">
-        <v>6720705</v>
+        <v>6720709</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124373923</v>
+        <v>124374061</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,30 +1018,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467320</v>
+        <v>467334</v>
       </c>
       <c r="R5" t="n">
-        <v>6720727</v>
+        <v>6720705</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374100</v>
+        <v>124373923</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,39 +1133,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467303</v>
+        <v>467320</v>
       </c>
       <c r="R6" t="n">
-        <v>6720698</v>
+        <v>6720727</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1232,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374210</v>
+        <v>124374084</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,30 +1239,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467276</v>
+        <v>467339</v>
       </c>
       <c r="R7" t="n">
-        <v>6720709</v>
+        <v>6720715</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374100</v>
+        <v>124374210</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467303</v>
+        <v>467276</v>
       </c>
       <c r="R2" t="n">
-        <v>6720698</v>
+        <v>6720709</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374229</v>
+        <v>124374084</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467270</v>
+        <v>467339</v>
       </c>
       <c r="R3" t="n">
-        <v>6720712</v>
+        <v>6720715</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -882,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374210</v>
+        <v>124374100</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,30 +904,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467276</v>
+        <v>467303</v>
       </c>
       <c r="R4" t="n">
-        <v>6720709</v>
+        <v>6720698</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374061</v>
+        <v>124373923</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,39 +1019,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467334</v>
+        <v>467320</v>
       </c>
       <c r="R5" t="n">
-        <v>6720705</v>
+        <v>6720727</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1121,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124373923</v>
+        <v>124374061</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,30 +1125,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467320</v>
+        <v>467334</v>
       </c>
       <c r="R6" t="n">
-        <v>6720727</v>
+        <v>6720705</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1227,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374084</v>
+        <v>124374229</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,35 +1240,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467339</v>
+        <v>467270</v>
       </c>
       <c r="R7" t="n">
-        <v>6720715</v>
+        <v>6720712</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1319,7 +1320,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374210</v>
+        <v>124374100</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467276</v>
+        <v>467303</v>
       </c>
       <c r="R2" t="n">
-        <v>6720709</v>
+        <v>6720698</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374084</v>
+        <v>124373923</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +802,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467339</v>
+        <v>467320</v>
       </c>
       <c r="R3" t="n">
-        <v>6720715</v>
+        <v>6720727</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -892,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374100</v>
+        <v>124374061</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -927,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -944,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467303</v>
+        <v>467334</v>
       </c>
       <c r="R4" t="n">
-        <v>6720698</v>
+        <v>6720705</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1007,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124373923</v>
+        <v>124374229</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,30 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467320</v>
+        <v>467270</v>
       </c>
       <c r="R5" t="n">
-        <v>6720727</v>
+        <v>6720712</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,7 +1103,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374061</v>
+        <v>124374210</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,39 +1133,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467334</v>
+        <v>467276</v>
       </c>
       <c r="R6" t="n">
-        <v>6720705</v>
+        <v>6720709</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374229</v>
+        <v>124374084</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,35 +1239,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1276,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467270</v>
+        <v>467339</v>
       </c>
       <c r="R7" t="n">
-        <v>6720712</v>
+        <v>6720715</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1320,6 +1319,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -675,51 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374100</v>
+        <v>124374210</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467303</v>
+        <v>467276</v>
       </c>
       <c r="R2" t="n">
-        <v>6720698</v>
+        <v>6720709</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -790,42 +776,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124373923</v>
+        <v>124374229</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467320</v>
+        <v>467270</v>
       </c>
       <c r="R3" t="n">
-        <v>6720727</v>
+        <v>6720712</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,7 +863,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,12 +884,7 @@
         <v>124374061</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,47 +991,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374229</v>
+        <v>124374084</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467270</v>
+        <v>467339</v>
       </c>
       <c r="R5" t="n">
-        <v>6720712</v>
+        <v>6720715</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,6 +1078,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,42 +1097,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374210</v>
+        <v>124374100</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467276</v>
+        <v>467303</v>
       </c>
       <c r="R6" t="n">
-        <v>6720709</v>
+        <v>6720698</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1227,47 +1207,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374084</v>
+        <v>124373923</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467339</v>
+        <v>467320</v>
       </c>
       <c r="R7" t="n">
-        <v>6720715</v>
+        <v>6720727</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 13344-2025 artfynd.xlsx
+++ b/artfynd/A 13344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124374210</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124374229</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124374061</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124374084</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124374100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,8 +1335,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124373923</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>